--- a/artfynd/A 17770-2026 artfynd.xlsx
+++ b/artfynd/A 17770-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132426939</v>
+        <v>136815405</v>
       </c>
       <c r="B2" t="n">
-        <v>92245</v>
+        <v>92107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Getklövmyran, Getklövmyran, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579073</v>
+        <v>578608</v>
       </c>
       <c r="R2" t="n">
-        <v>7052518</v>
+        <v>7052061</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,51 +786,51 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132426939</t>
+          <t>https://artportalen.se/Sighting/136815405</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135484913</v>
+        <v>136817370</v>
       </c>
       <c r="B3" t="n">
-        <v>92244</v>
+        <v>83343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 km öst om Nedre Strömnäs, Ång</t>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578806</v>
+        <v>578699</v>
       </c>
       <c r="R3" t="n">
-        <v>7052166</v>
+        <v>7051984</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,48 +883,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>gammal naturskogsartad tallskog på storblockig höjd</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal hängande tallåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135484913</t>
+          <t>https://artportalen.se/Sighting/136817370</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132427040</v>
+        <v>136815438</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Getklövmyran, Getklövmyran, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579091</v>
+        <v>578612</v>
       </c>
       <c r="R4" t="n">
-        <v>7052498</v>
+        <v>7052062</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,16 +1010,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132427040</t>
+          <t>https://artportalen.se/Sighting/136815438</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132427116</v>
+        <v>136815484</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,14 +1047,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Getklövmyran, Getklövmyran, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579132</v>
+        <v>578630</v>
       </c>
       <c r="R5" t="n">
-        <v>7052472</v>
+        <v>7052048</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,22 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,60 +1122,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132427116</t>
+          <t>https://artportalen.se/Sighting/136815484</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132426455</v>
+        <v>136816394</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Getklövmyran, Getklövmyran, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578870</v>
+        <v>578650</v>
       </c>
       <c r="R6" t="n">
-        <v>7052344</v>
+        <v>7051997</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,22 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,56 +1234,51 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132426455</t>
+          <t>https://artportalen.se/Sighting/136816394</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132426909</v>
+        <v>136817414</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Getklövmyran, Getklövmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579075</v>
+        <v>578705</v>
       </c>
       <c r="R7" t="n">
-        <v>7052526</v>
+        <v>7052012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,27 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,56 +1346,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132426909</t>
+          <t>https://artportalen.se/Sighting/136817414</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134113905</v>
+        <v>136817486</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>79476</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Getklövmyran, Getklövmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579151</v>
+        <v>578712</v>
       </c>
       <c r="R8" t="n">
-        <v>7052413</v>
+        <v>7052043</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,27 +1417,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,60 +1458,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134113905</t>
+          <t>https://artportalen.se/Sighting/136817486</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132426369</v>
+        <v>136817549</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>79476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getklövmyran, Getklövmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578856</v>
+        <v>578809</v>
       </c>
       <c r="R9" t="n">
-        <v>7052309</v>
+        <v>7052091</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,22 +1529,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,7 +1570,2684 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136817549</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132426939</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>658</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579073</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7052518</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132426939</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136815100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92111</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>578555</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7052108</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136815100</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136814537</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83343</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>578465</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7052171</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814537</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136815078</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83343</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>578549</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7052113</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136815078</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135484913</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92244</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>1 km öst om Nedre Strömnäs, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>578806</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7052166</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>gammal naturskogsartad tallskog på storblockig höjd</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hängande tallåga</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484913</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132427040</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579091</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7052498</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132427040</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132427116</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579132</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7052472</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132427116</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136814508</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>578465</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7052174</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814508</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136814777</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>578494</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7052180</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814777</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136815136</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>578568</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7052115</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136815136</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136818247</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>578824</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7052186</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136818247</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136818859</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>579129</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7052480</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136818859</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136818911</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>579169</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7052454</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136818911</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136818931</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>579212</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7052411</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136818931</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132426455</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>578870</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7052344</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132426455</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136814513</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>578465</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7052174</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814513</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132426909</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>579075</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7052526</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132426909</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134113905</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>579151</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7052413</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113905</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136814729</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>578498</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7052171</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814729</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136814588</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>578471</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7052178</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814588</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132426369</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>578856</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7052309</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/132426369</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136814278</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>578443</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7052164</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814278</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136818588</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>578964</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7052333</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136818588</t>
         </is>
       </c>
     </row>
@@ -1629,6 +4261,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17770-2026 artfynd.xlsx
+++ b/artfynd/A 17770-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136815405</v>
       </c>
       <c r="B2" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136815100</v>
       </c>
       <c r="B11" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
